--- a/dist/成果/防治对象/测量表/360481002209110_常丰村下汪村/沟道纵断面成果表_AFAE900128H00000ZACS008.xlsx
+++ b/dist/成果/防治对象/测量表/360481002209110_常丰村下汪村/沟道纵断面成果表_AFAE900128H00000ZACS008.xlsx
@@ -794,7 +794,7 @@
         <v>23.529</v>
       </c>
       <c r="F11" s="22" t="n">
-        <v>23.87076755124311</v>
+        <v>23.7199059275706</v>
       </c>
       <c r="G11" s="23" t="n">
         <v>115.593211</v>
@@ -822,7 +822,7 @@
         <v>23.459</v>
       </c>
       <c r="F12" s="22" t="n">
-        <v>23.79833086099942</v>
+        <v>23.66862542174176</v>
       </c>
       <c r="G12" s="23" t="n">
         <v>115.59375</v>
@@ -850,7 +850,7 @@
         <v>23.394</v>
       </c>
       <c r="F13" s="22" t="n">
-        <v>23.50120456517454</v>
+        <v>23.49159983756104</v>
       </c>
       <c r="G13" s="23" t="n">
         <v>115.594413</v>
@@ -878,7 +878,7 @@
         <v>23.394</v>
       </c>
       <c r="F14" s="22" t="n">
-        <v>23.88351912083218</v>
+        <v>23.56666794541885</v>
       </c>
       <c r="G14" s="23" t="n">
         <v>115.595206</v>
@@ -906,7 +906,7 @@
         <v>23.368</v>
       </c>
       <c r="F15" s="22" t="n">
-        <v>23.81935010732908</v>
+        <v>23.57458253081956</v>
       </c>
       <c r="G15" s="23" t="n">
         <v>115.595742</v>
@@ -934,7 +934,7 @@
         <v>23.269</v>
       </c>
       <c r="F16" s="22" t="n">
-        <v>23.57974374918334</v>
+        <v>23.49719073459085</v>
       </c>
       <c r="G16" s="23" t="n">
         <v>115.596463</v>
@@ -962,7 +962,7 @@
         <v>23.211</v>
       </c>
       <c r="F17" s="22" t="n">
-        <v>23.25623480629692</v>
+        <v>23.28578348628835</v>
       </c>
       <c r="G17" s="23" t="n">
         <v>115.597029</v>
@@ -990,7 +990,7 @@
         <v>23.128</v>
       </c>
       <c r="F18" s="22" t="n">
-        <v>23.27095536734608</v>
+        <v>23.43517238518639</v>
       </c>
       <c r="G18" s="23" t="n">
         <v>115.597645</v>
@@ -1018,7 +1018,7 @@
         <v>22.95</v>
       </c>
       <c r="F19" s="22" t="n">
-        <v>23.06948661208403</v>
+        <v>23.19720913302294</v>
       </c>
       <c r="G19" s="23" t="n">
         <v>115.598124</v>
@@ -1046,7 +1046,7 @@
         <v>22.751</v>
       </c>
       <c r="F20" s="22" t="n">
-        <v>22.91131792168299</v>
+        <v>23.04514301437826</v>
       </c>
       <c r="G20" s="23" t="n">
         <v>115.59837</v>
@@ -1074,7 +1074,7 @@
         <v>22.658</v>
       </c>
       <c r="F21" s="22" t="n">
-        <v>22.95414399711964</v>
+        <v>22.80618169976863</v>
       </c>
       <c r="G21" s="23" t="n">
         <v>115.598945</v>
@@ -1102,7 +1102,7 @@
         <v>22.457</v>
       </c>
       <c r="F22" s="22" t="n">
-        <v>22.71440972173414</v>
+        <v>22.80529638253259</v>
       </c>
       <c r="G22" s="23" t="n">
         <v>115.599555</v>
@@ -1130,7 +1130,7 @@
         <v>22.416</v>
       </c>
       <c r="F23" s="22" t="n">
-        <v>22.4333441695458</v>
+        <v>22.72337897974298</v>
       </c>
       <c r="G23" s="23" t="n">
         <v>115.60012</v>
@@ -1158,7 +1158,7 @@
         <v>22.401</v>
       </c>
       <c r="F24" s="22" t="n">
-        <v>22.41582234828336</v>
+        <v>22.67909853523655</v>
       </c>
       <c r="G24" s="23" t="n">
         <v>115.60061</v>
@@ -1186,7 +1186,7 @@
         <v>22.322</v>
       </c>
       <c r="F25" s="22" t="n">
-        <v>22.35855617849879</v>
+        <v>22.57155681731083</v>
       </c>
       <c r="G25" s="23" t="n">
         <v>115.601124</v>
@@ -1214,7 +1214,7 @@
         <v>22.268</v>
       </c>
       <c r="F26" s="22" t="n">
-        <v>22.29787354436128</v>
+        <v>22.49912987077953</v>
       </c>
       <c r="G26" s="23" t="n">
         <v>115.601758</v>
@@ -1242,7 +1242,7 @@
         <v>22.238</v>
       </c>
       <c r="F27" s="22" t="n">
-        <v>22.28443064595241</v>
+        <v>22.2934013161144</v>
       </c>
       <c r="G27" s="23" t="n">
         <v>115.602209</v>
@@ -1266,16 +1266,16 @@
     <mergeCell ref="D3:H3"/>
   </mergeCells>
   <dataValidations count="4">
-    <dataValidation sqref="D2:H2" showDropDown="0" showInputMessage="1" showErrorMessage="1" allowBlank="1" type="list">
+    <dataValidation sqref="D2:H2" showDropDown="0" showInputMessage="1" showErrorMessage="1" allowBlank="0" type="list">
       <formula1>"A,B"</formula1>
     </dataValidation>
-    <dataValidation sqref="B5" showDropDown="0" showInputMessage="1" showErrorMessage="1" allowBlank="1" type="list">
+    <dataValidation sqref="B5" showDropDown="0" showInputMessage="1" showErrorMessage="1" allowBlank="0" type="list">
       <formula1>"是,否"</formula1>
     </dataValidation>
-    <dataValidation sqref="B7" showDropDown="0" showInputMessage="1" showErrorMessage="1" allowBlank="1" type="list">
+    <dataValidation sqref="B7" showDropDown="0" showInputMessage="1" showErrorMessage="1" allowBlank="0" type="list">
       <formula1>"85高程系,假定高程系"</formula1>
     </dataValidation>
-    <dataValidation sqref="D7:H7" showDropDown="0" showInputMessage="1" showErrorMessage="1" allowBlank="1" type="list">
+    <dataValidation sqref="D7:H7" showDropDown="0" showInputMessage="1" showErrorMessage="1" allowBlank="0" type="list">
       <formula1>"水准仪／卷尺测量法,GNSS RTK测量法,全站仪法,三维激光扫描方法"</formula1>
     </dataValidation>
   </dataValidations>
